--- a/src/pages/data/Datos.xlsx
+++ b/src/pages/data/Datos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="226">
   <si>
     <t>First Name</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>john-cintron2599@hotmail.com</t>
+  </si>
+  <si>
+    <t>Q47487-04719</t>
   </si>
   <si>
     <t>Gitty</t>
@@ -741,7 +744,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -768,12 +771,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFA500"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -880,7 +877,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -916,9 +913,14 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -927,14 +929,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1358,7 +1352,9 @@
       <c r="M4" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="N4" s="21"/>
+      <c r="N4" s="16" t="s">
+        <v>42</v>
+      </c>
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
       <c r="Q4" s="15"/>
@@ -1373,19 +1369,19 @@
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C5" s="18">
         <v>19225</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5" s="19">
         <v>812</v>
@@ -1397,22 +1393,22 @@
         <v>28</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L5" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M5" s="17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N5" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O5" s="15"/>
       <c r="P5" s="15"/>
@@ -1428,19 +1424,19 @@
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" s="18">
         <v>24391</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F6" s="19">
         <v>641</v>
@@ -1455,19 +1451,19 @@
         <v>29</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L6" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M6" s="17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N6" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O6" s="15"/>
       <c r="P6" s="15"/>
@@ -1483,19 +1479,19 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" s="18">
         <v>29287</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F7" s="19">
         <v>814</v>
@@ -1507,22 +1503,22 @@
         <v>28</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L7" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M7" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N7" s="16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
@@ -1538,19 +1534,19 @@
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" s="18">
         <v>19819</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F8" s="19">
         <v>651</v>
@@ -1562,19 +1558,19 @@
         <v>28</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L8" s="17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N8" s="16"/>
       <c r="O8" s="15"/>
@@ -1591,19 +1587,19 @@
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C9" s="18">
         <v>30760</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F9" s="19">
         <v>295</v>
@@ -1618,16 +1614,16 @@
         <v>38</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M9" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N9" s="16"/>
       <c r="O9" s="15"/>
@@ -1644,19 +1640,19 @@
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" s="18">
         <v>22868</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F10" s="19">
         <v>529</v>
@@ -1668,19 +1664,19 @@
         <v>28</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10" s="20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L10" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M10" s="17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N10" s="16"/>
       <c r="O10" s="15"/>
@@ -1697,19 +1693,19 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11" s="18">
         <v>33755</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F11" s="19">
         <v>164</v>
@@ -1721,19 +1717,19 @@
         <v>28</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M11" s="17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N11" s="16"/>
       <c r="O11" s="15"/>
@@ -1750,43 +1746,43 @@
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="18">
         <v>22238</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F12" s="19">
         <v>874</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>28</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N12" s="16"/>
       <c r="O12" s="15"/>
@@ -1802,44 +1798,44 @@
       <c r="Y12" s="15"/>
     </row>
     <row r="13" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" s="22" t="s">
+      <c r="A13" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="23">
+      <c r="B13" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="22">
         <v>18533</v>
       </c>
-      <c r="D13" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="E13" s="22" t="s">
+      <c r="D13" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="F13" s="24">
+      <c r="E13" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="F13" s="23">
         <v>557</v>
       </c>
-      <c r="G13" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="H13" s="22" t="s">
+      <c r="G13" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="H13" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="J13" s="25" t="s">
+      <c r="I13" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="K13" s="22" t="s">
+      <c r="J13" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="L13" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="M13" s="22" t="s">
+      <c r="K13" s="21" t="s">
         <v>115</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>116</v>
       </c>
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
@@ -1855,44 +1851,44 @@
       <c r="Y13" s="7"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="B14" s="26" t="s">
+      <c r="A14" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="27">
+      <c r="B14" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="26">
         <v>34730</v>
       </c>
-      <c r="D14" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" s="26" t="s">
+      <c r="D14" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="F14" s="28">
+      <c r="E14" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14" s="27">
         <v>522</v>
       </c>
-      <c r="G14" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="H14" s="26" t="s">
+      <c r="G14" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="H14" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="J14" s="29" t="s">
+      <c r="I14" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="K14" s="26" t="s">
+      <c r="J14" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="L14" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="M14" s="26" t="s">
+      <c r="K14" s="25" t="s">
         <v>123</v>
+      </c>
+      <c r="L14" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="M14" s="25" t="s">
+        <v>124</v>
       </c>
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
@@ -1908,44 +1904,44 @@
       <c r="Y14" s="7"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="B15" s="22" t="s">
+      <c r="A15" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="C15" s="23">
+      <c r="B15" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" s="22">
         <v>25419</v>
       </c>
-      <c r="D15" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="E15" s="22" t="s">
+      <c r="D15" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="F15" s="24">
+      <c r="E15" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="F15" s="23">
         <v>217</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I15" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="J15" s="25" t="s">
+      <c r="I15" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="K15" s="22" t="s">
+      <c r="J15" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="L15" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="M15" s="22" t="s">
+      <c r="K15" s="21" t="s">
         <v>131</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="M15" s="21" t="s">
+        <v>132</v>
       </c>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
@@ -1961,44 +1957,44 @@
       <c r="Y15" s="7"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" s="27">
+      <c r="A16" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C16" s="26">
         <v>28973</v>
       </c>
-      <c r="D16" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="E16" s="26" t="s">
+      <c r="D16" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="F16" s="28">
+      <c r="E16" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="F16" s="27">
         <v>156</v>
       </c>
-      <c r="G16" s="26" t="s">
+      <c r="G16" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="H16" s="26" t="s">
+      <c r="H16" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="I16" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="J16" s="29" t="s">
+      <c r="I16" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="K16" s="26" t="s">
+      <c r="J16" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="L16" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="M16" s="26" t="s">
+      <c r="K16" s="25" t="s">
         <v>138</v>
+      </c>
+      <c r="L16" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="M16" s="25" t="s">
+        <v>139</v>
       </c>
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
@@ -2014,44 +2010,44 @@
       <c r="Y16" s="7"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="B17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="27">
+      <c r="B17" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="26">
         <v>29989</v>
       </c>
-      <c r="D17" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="E17" s="26" t="s">
+      <c r="D17" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="F17" s="28">
+      <c r="E17" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="F17" s="27">
         <v>499</v>
       </c>
-      <c r="G17" s="26" t="s">
+      <c r="G17" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="H17" s="26" t="s">
+      <c r="H17" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="J17" s="29" t="s">
+      <c r="I17" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="J17" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="L17" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="M17" s="26" t="s">
+      <c r="K17" s="25" t="s">
         <v>146</v>
+      </c>
+      <c r="L17" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="M17" s="25" t="s">
+        <v>147</v>
       </c>
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
@@ -2067,44 +2063,44 @@
       <c r="Y17" s="7"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="B18" s="22" t="s">
+      <c r="A18" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="C18" s="23">
+      <c r="B18" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="C18" s="22">
         <v>20751</v>
       </c>
-      <c r="D18" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="E18" s="22" t="s">
+      <c r="D18" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="F18" s="24">
+      <c r="E18" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="F18" s="23">
         <v>412</v>
       </c>
-      <c r="G18" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="H18" s="22" t="s">
+      <c r="G18" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I18" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="J18" s="25" t="s">
+      <c r="I18" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="K18" s="22" t="s">
+      <c r="J18" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="L18" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="M18" s="22" t="s">
+      <c r="K18" s="21" t="s">
         <v>154</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="M18" s="21" t="s">
+        <v>155</v>
       </c>
       <c r="N18" s="7"/>
       <c r="O18" s="7"/>
@@ -2120,44 +2116,44 @@
       <c r="Y18" s="7"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="B19" s="26" t="s">
+      <c r="A19" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="C19" s="27">
+      <c r="B19" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="C19" s="26">
         <v>31548</v>
       </c>
-      <c r="D19" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="E19" s="26" t="s">
+      <c r="D19" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="F19" s="28">
+      <c r="E19" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="F19" s="27">
         <v>603</v>
       </c>
-      <c r="G19" s="26" t="s">
+      <c r="G19" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="H19" s="26" t="s">
+      <c r="H19" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="I19" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="J19" s="29" t="s">
+      <c r="I19" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="K19" s="26" t="s">
+      <c r="J19" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="L19" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="M19" s="26" t="s">
+      <c r="K19" s="25" t="s">
         <v>162</v>
+      </c>
+      <c r="L19" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="M19" s="25" t="s">
+        <v>163</v>
       </c>
       <c r="N19" s="7"/>
       <c r="O19" s="7"/>
@@ -2173,44 +2169,44 @@
       <c r="Y19" s="7"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A20" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="B20" s="22" t="s">
+      <c r="A20" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="C20" s="23">
+      <c r="B20" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="C20" s="22">
         <v>30398</v>
       </c>
-      <c r="D20" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="E20" s="22" t="s">
+      <c r="D20" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="F20" s="24">
+      <c r="E20" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="F20" s="23">
         <v>935</v>
       </c>
-      <c r="G20" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="H20" s="22" t="s">
+      <c r="G20" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I20" s="22" t="s">
-        <v>167</v>
-      </c>
-      <c r="J20" s="25" t="s">
+      <c r="I20" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="K20" s="22" t="s">
+      <c r="J20" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="L20" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="M20" s="22" t="s">
+      <c r="K20" s="21" t="s">
         <v>170</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="M20" s="21" t="s">
+        <v>171</v>
       </c>
       <c r="N20" s="7"/>
       <c r="O20" s="7"/>
@@ -2226,44 +2222,44 @@
       <c r="Y20" s="7"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="B21" s="26" t="s">
+      <c r="A21" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="C21" s="27">
+      <c r="B21" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="26">
         <v>26305</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="E21" s="26" t="s">
+      <c r="D21" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="F21" s="28">
+      <c r="E21" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="F21" s="27">
         <v>861</v>
       </c>
-      <c r="G21" s="26" t="s">
+      <c r="G21" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="H21" s="26" t="s">
+      <c r="H21" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="J21" s="29" t="s">
+      <c r="I21" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="K21" s="26" t="s">
+      <c r="J21" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="L21" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="M21" s="26" t="s">
+      <c r="K21" s="25" t="s">
         <v>178</v>
+      </c>
+      <c r="L21" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="M21" s="25" t="s">
+        <v>179</v>
       </c>
       <c r="N21" s="7"/>
       <c r="O21" s="7"/>
@@ -2279,44 +2275,44 @@
       <c r="Y21" s="7"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="B22" s="22" t="s">
+      <c r="A22" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="C22" s="23">
+      <c r="B22" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C22" s="22">
         <v>21956</v>
       </c>
-      <c r="D22" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="E22" s="22" t="s">
+      <c r="D22" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="F22" s="24">
+      <c r="E22" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="F22" s="23">
         <v>947</v>
       </c>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="H22" s="22" t="s">
+      <c r="H22" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I22" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="J22" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="K22" s="22" t="s">
+      <c r="I22" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="J22" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="L22" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="M22" s="22" t="s">
+      <c r="K22" s="21" t="s">
         <v>185</v>
+      </c>
+      <c r="L22" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="M22" s="21" t="s">
+        <v>186</v>
       </c>
       <c r="N22" s="7"/>
       <c r="O22" s="7"/>
@@ -2332,44 +2328,44 @@
       <c r="Y22" s="7"/>
     </row>
     <row r="23" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="B23" s="26" t="s">
+      <c r="A23" s="25" t="s">
         <v>187</v>
       </c>
-      <c r="C23" s="27">
+      <c r="B23" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" s="26">
         <v>24146</v>
       </c>
-      <c r="D23" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="E23" s="26" t="s">
+      <c r="D23" s="25" t="s">
         <v>189</v>
       </c>
-      <c r="F23" s="28">
+      <c r="E23" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="F23" s="27">
         <v>123</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="H23" s="26" t="s">
+      <c r="H23" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="I23" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="J23" s="29" t="s">
+      <c r="I23" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="K23" s="26" t="s">
+      <c r="J23" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="L23" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="M23" s="26" t="s">
+      <c r="K23" s="25" t="s">
         <v>193</v>
+      </c>
+      <c r="L23" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="M23" s="25" t="s">
+        <v>194</v>
       </c>
       <c r="N23" s="7"/>
       <c r="O23" s="7"/>
@@ -2385,44 +2381,44 @@
       <c r="Y23" s="7"/>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A24" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="B24" s="22" t="s">
+      <c r="A24" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="C24" s="23">
+      <c r="B24" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="C24" s="22">
         <v>23221</v>
       </c>
-      <c r="D24" s="22" t="s">
-        <v>196</v>
-      </c>
-      <c r="E24" s="22" t="s">
+      <c r="D24" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="F24" s="24">
+      <c r="E24" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F24" s="23">
         <v>936</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="H24" s="22" t="s">
+      <c r="H24" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I24" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="J24" s="25" t="s">
+      <c r="I24" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="K24" s="22" t="s">
+      <c r="J24" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="L24" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="M24" s="22" t="s">
+      <c r="K24" s="21" t="s">
         <v>201</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="M24" s="21" t="s">
+        <v>202</v>
       </c>
       <c r="N24" s="7"/>
       <c r="O24" s="7"/>
@@ -2438,44 +2434,44 @@
       <c r="Y24" s="7"/>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="B25" s="26" t="s">
+      <c r="A25" s="25" t="s">
         <v>203</v>
       </c>
-      <c r="C25" s="27">
+      <c r="B25" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="C25" s="26">
         <v>33638</v>
       </c>
-      <c r="D25" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="E25" s="26" t="s">
+      <c r="D25" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="F25" s="28">
+      <c r="E25" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="F25" s="27">
         <v>482</v>
       </c>
-      <c r="G25" s="26" t="s">
+      <c r="G25" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="H25" s="26" t="s">
+      <c r="H25" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="I25" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="J25" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="K25" s="26" t="s">
+      <c r="I25" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="J25" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="L25" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="M25" s="26" t="s">
+      <c r="K25" s="25" t="s">
         <v>208</v>
+      </c>
+      <c r="L25" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="M25" s="25" t="s">
+        <v>209</v>
       </c>
       <c r="N25" s="7"/>
       <c r="O25" s="7"/>
@@ -2491,44 +2487,44 @@
       <c r="Y25" s="7"/>
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A26" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="B26" s="22" t="s">
+      <c r="A26" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="C26" s="23">
+      <c r="B26" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="C26" s="22">
         <v>26113</v>
       </c>
-      <c r="D26" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="E26" s="22" t="s">
+      <c r="D26" s="21" t="s">
         <v>212</v>
       </c>
-      <c r="F26" s="24">
+      <c r="E26" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="F26" s="23">
         <v>316</v>
       </c>
-      <c r="G26" s="22" t="s">
+      <c r="G26" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="H26" s="22" t="s">
+      <c r="H26" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I26" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="J26" s="25" t="s">
+      <c r="I26" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="K26" s="22" t="s">
+      <c r="J26" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="L26" s="22" t="s">
-        <v>215</v>
-      </c>
-      <c r="M26" s="22" t="s">
+      <c r="K26" s="21" t="s">
         <v>216</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="M26" s="21" t="s">
+        <v>217</v>
       </c>
       <c r="N26" s="7"/>
       <c r="O26" s="7"/>
@@ -2544,44 +2540,44 @@
       <c r="Y26" s="7"/>
     </row>
     <row r="27" ht="15.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A27" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="B27" s="26" t="s">
+      <c r="A27" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="C27" s="27">
+      <c r="B27" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="C27" s="26">
         <v>28022</v>
       </c>
-      <c r="D27" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="E27" s="26" t="s">
+      <c r="D27" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="F27" s="28">
+      <c r="E27" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="F27" s="27">
         <v>782</v>
       </c>
-      <c r="G27" s="26" t="s">
+      <c r="G27" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="H27" s="26" t="s">
+      <c r="H27" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="I27" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="J27" s="29" t="s">
+      <c r="I27" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="K27" s="26" t="s">
+      <c r="J27" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="L27" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="M27" s="26" t="s">
+      <c r="K27" s="25" t="s">
         <v>224</v>
+      </c>
+      <c r="L27" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="M27" s="25" t="s">
+        <v>225</v>
       </c>
       <c r="N27" s="7"/>
       <c r="O27" s="7"/>
